--- a/University_project/Fly_mechanics/Projet_L3/feuille_activités_2026.xlsx
+++ b/University_project/Fly_mechanics/Projet_L3/feuille_activités_2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Etudiant_1" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="167">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t xml:space="preserve">1- remplir identité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WOLI Friedly</t>
   </si>
   <si>
     <t xml:space="preserve">2 - remplir les tâches, une ligne par étudiants.  Si les étudiants ont travaillé ensemble mettre deux lignes en recopiant l'activité, le travail sera comptabilisé par étudiants, il doit y avoir des tâches spécifiques à chaque étudiant parfois</t>
@@ -200,7 +203,7 @@
     <t xml:space="preserve">échange sur l’évolution du projet</t>
   </si>
   <si>
-    <t xml:space="preserve">Amélioration de la structure du projet en testant la focntionalité du code </t>
+    <t xml:space="preserve">Amélioration de la structure du projet , Mettre en commun les idées, revoir la déclaration des variables du code</t>
   </si>
   <si>
     <t xml:space="preserve">https://drive.google.com/drive/folders/1jt_jbpEzWI36Kqa891_FEtaVIgAmSU8a</t>
@@ -218,22 +221,31 @@
     <t xml:space="preserve">1h</t>
   </si>
   <si>
-    <t xml:space="preserve">Un peu de recherche à la Bu en plus du codage de la fonction distance_resumé</t>
+    <t xml:space="preserve">Un peu de recherche à la BU, en plus du codage de la fonction de distance de décollage selon le livre Mechanics of Flight de Warren F. Phillips.</t>
   </si>
   <si>
     <t xml:space="preserve">Rapport</t>
   </si>
   <si>
+    <t xml:space="preserve">Présentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les autres tâches</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Vendredi 15 mai 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Transforme mon code en classe, remplis les tableaux, définis les entrées, les unités et les éléments de convection, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Présentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les autres tâches</t>
+    <t xml:space="preserve">4h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transforme mon code (fonctions def simples) en classe, remplis les tableaux Excel en définissant les entrées avec leurs unités et les éléments de conversion, dans la feuille Déclaration des variables. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samedi 16 mai 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Étude de nouvelle méthode de calcul de la distance dans le livre General Aviation Aircraft Design à la bibliothèque</t>
   </si>
   <si>
     <t xml:space="preserve">Durée total du travail</t>
@@ -627,13 +639,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$-40C]dd\-mmm"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="167" formatCode="0.00\ %"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
+    <numFmt numFmtId="168" formatCode="0.00\ %"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -734,6 +747,11 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
@@ -753,6 +771,7 @@
       <sz val="10"/>
       <name val="Courier New"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -885,280 +904,296 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1458,597 +1493,603 @@
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="44.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="8" style="0" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="19.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="41.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="44.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="8" style="1" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="G4" s="15" t="s">
         <v>13</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="D5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>18</v>
       </c>
+      <c r="G5" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="19" t="n">
+      <c r="A6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="20" t="n">
         <v>46157</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21" t="s">
+      <c r="C6" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="D6" s="22"/>
+      <c r="E6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0" t="s">
+      <c r="F6" s="23" t="s">
         <v>23</v>
       </c>
+      <c r="G6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="23"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-      <c r="I8" s="0" t="s">
-        <v>24</v>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24"/>
+      <c r="I8" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="23"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="B13" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="29" t="s">
+      <c r="C13" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32" t="n">
+      <c r="D13" s="31"/>
+      <c r="E13" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="32"/>
+      <c r="G13" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="32"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="32"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="32"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="33"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37" t="s">
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="40"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="36"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="41"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="36"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="41"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="36"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="41"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="36"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="41"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="36"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="41"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="39"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="39"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="39"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="39"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40" t="s">
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="42"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="46"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="s">
+      <c r="B31" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="49"/>
+      <c r="C31" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="50"/>
+      <c r="E31" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" s="52"/>
+      <c r="G31" s="53" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="45"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="50"/>
+      <c r="E32" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="52"/>
+      <c r="G32" s="54"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="45"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="49"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="54"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="49"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="54"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="45"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="49"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="54"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="45"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="54"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="45"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="49"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="54"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="45"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="49"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="54"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="45"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="49"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="54"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="45"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="49"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="54"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="45"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="49"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="54"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="45"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="49"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="54"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="45"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="49"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="54"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="45"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="49"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="54"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="45"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="49"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="54"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="45"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="49"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="54"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="45"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="49"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="54"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="45"/>
-      <c r="B48" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="49"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="49"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="54"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="45"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="49"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="54"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="45"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="49"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="54"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="45"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="49"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="54"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B54" s="50" t="n">
+      <c r="A54" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <f aca="false">SUM(C6:C51)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="53" t="n">
+      <c r="A55" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="58" t="n">
         <f aca="false">C54/B54</f>
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2082,574 +2123,574 @@
   <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="38.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="44.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="8" style="0" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="19.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="41.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="38.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="44.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="8" style="1" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>6</v>
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="14" t="s">
         <v>12</v>
       </c>
+      <c r="G4" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="D5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>18</v>
       </c>
+      <c r="G5" s="18" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23"/>
+      <c r="A6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="23"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="23"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
+      <c r="A13" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="31"/>
+      <c r="E13" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="32"/>
+      <c r="G13" s="33"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="32"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="33"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="32"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="32"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="32"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="33"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="27"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
+      <c r="A22" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="41"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="41"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="35"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="39"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="41"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="39"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="41"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="39"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="39"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="41"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="42"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="46"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="46"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="44"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="44"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="49"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="45"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="46"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="49"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="54"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="45"/>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="49"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="54"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="49"/>
+      <c r="A34" s="47"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="54"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="45"/>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="49"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="54"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="45"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="54"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="45"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="49"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="54"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="45"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="49"/>
+      <c r="A38" s="47"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="54"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="45"/>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="49"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="54"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="45"/>
-      <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="49"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="54"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="45"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="49"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="54"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="45"/>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="49"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="54"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="45"/>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="49"/>
+      <c r="A43" s="47"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="54"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="45"/>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="49"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="54"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="45"/>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="49"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="54"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="45"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="49"/>
+      <c r="A46" s="47"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="54"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="45"/>
-      <c r="B47" s="46"/>
-      <c r="C47" s="46"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="49"/>
+      <c r="A47" s="47"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="54"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="45"/>
-      <c r="B48" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="49"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="49"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="54"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="45"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="49"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="54"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="45"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="49"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="54"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="45"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="49"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="54"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B54" s="50" t="n">
+      <c r="A54" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="55" t="n">
         <v>100</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <f aca="false">SUM(C6:C51)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="53" t="n">
+      <c r="A55" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="58" t="n">
         <f aca="false">C54/B54</f>
         <v>0</v>
       </c>
@@ -2685,383 +2726,383 @@
   <dimension ref="A1:E70"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="55"/>
+      <c r="A1" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="60"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="54" t="s">
-        <v>40</v>
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>41</v>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>43</v>
+      <c r="B5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="61" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>45</v>
+      <c r="B6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="0" t="s">
-        <v>46</v>
+      <c r="E7" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="0" t="s">
-        <v>47</v>
+      <c r="E8" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="0" t="s">
-        <v>48</v>
+      <c r="E9" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>50</v>
+      <c r="A10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>53</v>
+      <c r="B11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>55</v>
+      <c r="B12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>57</v>
+      <c r="B13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>59</v>
+      <c r="B14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>61</v>
+      <c r="B15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>62</v>
+      <c r="B17" s="4" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="57"/>
+      <c r="B18" s="62" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="62"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="57" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="57"/>
+      <c r="B19" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="62"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>65</v>
+      <c r="A23" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="57"/>
+      <c r="B24" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="62"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="57"/>
+      <c r="B25" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="62"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="57"/>
+      <c r="B26" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="62"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="57"/>
+      <c r="B27" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="62"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="57"/>
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="62"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="57"/>
+      <c r="B32" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="62"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="58"/>
+      <c r="B33" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="63"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="58" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" s="58"/>
+      <c r="B34" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="63"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" s="57"/>
+      <c r="B35" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="62"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="57"/>
+      <c r="B36" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="62"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="58" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="58"/>
+      <c r="B37" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="63"/>
     </row>
     <row r="38" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="59"/>
+      <c r="B38" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="64"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="59" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="59"/>
+      <c r="B39" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="64"/>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="60"/>
-      <c r="C40" s="60"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="57"/>
+      <c r="A42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="62"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="C43" s="61"/>
+      <c r="B43" s="66" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="66"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="57"/>
+      <c r="B44" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="62"/>
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="62" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="62"/>
+      <c r="B45" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="67"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>84</v>
+      <c r="A48" s="4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" s="58"/>
+      <c r="B49" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="63"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" s="58"/>
+      <c r="B50" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="63"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="63"/>
-      <c r="C51" s="63"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="68"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
-        <v>87</v>
+      <c r="A54" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="B55" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="59"/>
+      <c r="A55" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="C55" s="64"/>
     </row>
     <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="B56" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="57"/>
+      <c r="A56" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" s="62"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="65"/>
-      <c r="B57" s="57" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="57"/>
+      <c r="A57" s="70"/>
+      <c r="B57" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="C57" s="62"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="65"/>
-      <c r="B58" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" s="57"/>
+      <c r="A58" s="70"/>
+      <c r="B58" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="C58" s="62"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="65"/>
-      <c r="B59" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" s="58"/>
+      <c r="A59" s="70"/>
+      <c r="B59" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" s="63"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="65"/>
-      <c r="B60" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="66"/>
+      <c r="A60" s="70"/>
+      <c r="B60" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="C60" s="61"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="65"/>
-      <c r="B61" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" s="58"/>
+      <c r="A61" s="70"/>
+      <c r="B61" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" s="63"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="65"/>
-      <c r="B62" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="C62" s="57"/>
+      <c r="A62" s="70"/>
+      <c r="B62" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="62"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="65"/>
+      <c r="A63" s="70"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="65" t="s">
-        <v>97</v>
-      </c>
-      <c r="B64" s="58" t="s">
-        <v>98</v>
-      </c>
-      <c r="C64" s="58"/>
+      <c r="A64" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B64" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="63"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" s="58"/>
+      <c r="B65" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" s="63"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="58" t="s">
-        <v>100</v>
-      </c>
-      <c r="C66" s="58"/>
+      <c r="B66" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="C66" s="63"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="58" t="s">
-        <v>101</v>
-      </c>
-      <c r="C67" s="58"/>
+      <c r="B67" s="63" t="s">
+        <v>105</v>
+      </c>
+      <c r="C67" s="63"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="58" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="58"/>
+      <c r="B68" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="63"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="C69" s="58"/>
+      <c r="B69" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="C69" s="63"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="58" t="s">
-        <v>104</v>
-      </c>
-      <c r="C70" s="58"/>
+      <c r="B70" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -3124,333 +3165,333 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="67"/>
+      <c r="I2" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="J2" s="71"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="I3" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>109</v>
+      <c r="B3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="I3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="68" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="I5" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>113</v>
+      <c r="B5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="I5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="68" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="I6" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>117</v>
+      <c r="B6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="I6" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="I7" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>121</v>
+      <c r="B7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="I7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="67" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="I8" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>125</v>
+      <c r="B8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="71"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="71"/>
+      <c r="I8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="68" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
+      <c r="B9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="68" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
+      <c r="B10" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
+      <c r="B11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
+      <c r="G11" s="72"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="68" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
+      <c r="B12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
+      <c r="B13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="72" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="72"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="72"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="72" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="67" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
+      <c r="C17" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="I18" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="J18" s="0" t="s">
-        <v>146</v>
+      <c r="B18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="I18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="C19" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="I19" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="J19" s="0" t="s">
-        <v>146</v>
+      <c r="B19" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="I19" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="72"/>
+      <c r="I20" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="J20" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="I20" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="J20" s="0" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="68" t="s">
-        <v>152</v>
-      </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="I21" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="0" t="s">
-        <v>146</v>
+      <c r="B21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="72" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="I21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="I22" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="J22" s="0" t="s">
-        <v>156</v>
+      <c r="B22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="I22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="C23" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="I23" s="0" t="s">
+      <c r="B23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="72" t="s">
         <v>158</v>
       </c>
-      <c r="J23" s="0" t="s">
-        <v>159</v>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="I23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="68"/>
-      <c r="I24" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="J24" s="0" t="s">
-        <v>162</v>
+      <c r="B24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="I24" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
